--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.28584765694283</v>
+        <v>1.996450244253209</v>
       </c>
       <c r="D2" t="n">
-        <v>9.73075971995967</v>
+        <v>1.581248454493446</v>
       </c>
       <c r="E2" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F2" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.16398441861418</v>
+        <v>2.301647468024804</v>
       </c>
       <c r="D3" t="n">
-        <v>11.82083074094407</v>
+        <v>1.920884995403411</v>
       </c>
       <c r="E3" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F3" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.92962546454247</v>
+        <v>2.263564137988152</v>
       </c>
       <c r="D4" t="n">
-        <v>13.82528997311338</v>
+        <v>2.246609620630924</v>
       </c>
       <c r="E4" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F4" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.19715921639132</v>
+        <v>2.30703837266359</v>
       </c>
       <c r="D5" t="n">
-        <v>15.13544053711543</v>
+        <v>2.459509087281257</v>
       </c>
       <c r="E5" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F5" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.68427348408119</v>
+        <v>5.636194441163194</v>
       </c>
       <c r="D6" t="n">
-        <v>5.639526668726925</v>
+        <v>0.9164230836681254</v>
       </c>
       <c r="E6" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F6" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.305957195271</v>
+        <v>5.574718044231537</v>
       </c>
       <c r="D7" t="n">
-        <v>35.52828146663208</v>
+        <v>5.773345738327714</v>
       </c>
       <c r="E7" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F7" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.19257206587454</v>
+        <v>4.743792960704614</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62909614791302</v>
+        <v>4.977228124035866</v>
       </c>
       <c r="E8" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F8" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.36202636589228</v>
+        <v>5.908829284457497</v>
       </c>
       <c r="D9" t="n">
-        <v>35.73681328386885</v>
+        <v>5.807232158628688</v>
       </c>
       <c r="E9" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F9" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15902662867737</v>
+        <v>6.038341827160072</v>
       </c>
       <c r="D10" t="n">
-        <v>22.337426995425</v>
+        <v>3.629831886756563</v>
       </c>
       <c r="E10" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F10" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.39669376221961</v>
+        <v>4.451962736360687</v>
       </c>
       <c r="D11" t="n">
-        <v>26.74800035091324</v>
+        <v>4.346550057023401</v>
       </c>
       <c r="E11" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F11" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.1752122646069</v>
+        <v>6.853471992998621</v>
       </c>
       <c r="D12" t="n">
-        <v>39.39643627358791</v>
+        <v>6.401920894458035</v>
       </c>
       <c r="E12" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F12" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.50398570008688</v>
+        <v>3.169397676264118</v>
       </c>
       <c r="D13" t="n">
-        <v>15.860887557643</v>
+        <v>2.577394228116988</v>
       </c>
       <c r="E13" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F13" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.18584371707971</v>
+        <v>3.930199604025452</v>
       </c>
       <c r="D14" t="n">
-        <v>19.91868487721157</v>
+        <v>3.23678629254688</v>
       </c>
       <c r="E14" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F14" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.28237511584772</v>
+        <v>3.945885956325255</v>
       </c>
       <c r="D15" t="n">
-        <v>22.07753313009128</v>
+        <v>3.587599133639833</v>
       </c>
       <c r="E15" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F15" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.11836505614558</v>
+        <v>6.194234321623656</v>
       </c>
       <c r="D16" t="n">
-        <v>38.58703672064473</v>
+        <v>6.270393467104769</v>
       </c>
       <c r="E16" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F16" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41006224142573</v>
+        <v>5.754135114231681</v>
       </c>
       <c r="D17" t="n">
-        <v>33.87933430648756</v>
+        <v>5.50539182480423</v>
       </c>
       <c r="E17" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F17" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.30079792130608</v>
+        <v>7.686379662212239</v>
       </c>
       <c r="D18" t="n">
-        <v>43.52144331569665</v>
+        <v>7.072234538800706</v>
       </c>
       <c r="E18" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F18" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.49038339317311</v>
+        <v>7.229687301390631</v>
       </c>
       <c r="D19" t="n">
-        <v>43.2122425506013</v>
+        <v>7.021989414472712</v>
       </c>
       <c r="E19" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F19" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>37.77666546724025</v>
+        <v>6.138708138426541</v>
       </c>
       <c r="D20" t="n">
-        <v>36.48802502417158</v>
+        <v>5.929304066427881</v>
       </c>
       <c r="E20" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F20" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>16.64567022762385</v>
+        <v>2.704921411988875</v>
       </c>
       <c r="D21" t="n">
-        <v>15.49341290934056</v>
+        <v>2.517679597767841</v>
       </c>
       <c r="E21" t="n">
-        <v>10.87858462235896</v>
+        <v>1.767770001133332</v>
       </c>
       <c r="F21" t="n">
-        <v>11.71614790036366</v>
+        <v>1.903874033809094</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
